--- a/processed_ruby_restored_xlsx/sc242_みるく４：自由研究.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc242_みるく４：自由研究.ss.xlsx
@@ -1078,9 +1078,9 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>I'm not about to be all high-and-mighty and press her,
-but it bugs me that Miru-chan's so obviously trying to
-cover something up.</t>
+          <t>I'm not about to be all high-and-mighty and press
+her, but it bugs me that Miru-chan's so obviously
+trying to cover something up.</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1110,7 +1110,8 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... so, what's that you're holding in both hands？」</t>
+          <t>「Hmm... so, what's that you're holding in both
+hands？」</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1353,8 +1354,9 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, being naturally honest, ends up darting her
-eyes around nervously as she tries to play it off.</t>
+          <t>Miru-chan, being naturally honest, ends up darting
+her eyes around nervously as she tries to play it
+off.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1705,8 +1707,8 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan can't really get properly mad, so she groans
-awkwardly.</t>
+          <t>Miru-chan can't really get properly mad, so she
+groans awkwardly.</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2441,9 +2443,9 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>Maybe you kind of compare the way the fabric stretches
-and, from that, end up imagining the size... or
-rather...</t>
+          <t>Maybe you kind of compare the way the fabric
+stretches and, from that, end up imagining the
+size... or rather...</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2533,8 +2535,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>When I mentioned that she'd refused earlier, this time
-she nodded for me.</t>
+          <t>When I mentioned that she'd refused earlier, this
+time she nodded for me.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2549,8 +2551,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>I'm like that too, but even when you're joking around,
-you can still end up getting into it...！</t>
+          <t>I'm like that too, but even when you're joking
+around, you can still end up getting into it...！</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2749,7 +2751,8 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>「In the morning, it just gets hard on its own, right？」</t>
+          <t>「In the morning, it just gets hard on its own,
+right？」</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2930,8 +2933,8 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>After saying that, I silently ran my pencil across the
-page.</t>
+          <t>After saying that, I silently ran my pencil across
+the page.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3099,7 +3102,8 @@
       <c r="B173" s="1" t="inlineStr">
         <is>
           <t>When Miru-chan starts seriously working on her
-independent study, it just makes things harder for me.</t>
+independent study, it just makes things harder for
+me.</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3787,8 +3791,8 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>But then, as if she'd remembered something, she gently
-grabbed my penis.</t>
+          <t>But then, as if she'd remembered something, she
+gently grabbed my penis.</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -4172,8 +4176,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>Maybe my guess was right, but Miru-chan's getting into
-it more and more...？</t>
+          <t>Maybe my guess was right, but Miru-chan's getting
+into it more and more...？</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4585,8 +4589,8 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>I blurted it out, but I wondered if she'd still resist
-doing a fellatio….</t>
+          <t>I blurted it out, but I wondered if she'd still
+resist doing a fellatio….</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -5163,8 +5167,8 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>「Lero, lero！ Rererreru, nhah！ Nn... lero, lero, leroo,
-nn, n~！」</t>
+          <t>「Lero, lero！ Rererreru, nhah！ Nn... lero, lero,
+leroo, nn, n~！」</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5195,7 +5199,8 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>She just keeps trying, single-mindedly, to turn me on.</t>
+          <t>She just keeps trying, single-mindedly, to turn me
+on.</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5334,8 +5339,8 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>I stroked Miru-chan's head, trembling from the surging
-pleasure.</t>
+          <t>I stroked Miru-chan's head, trembling from the
+surging pleasure.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5425,8 +5430,8 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「Then I'll do more... amu, chu, rero, reroryu... nnya,
-rerorerorero~... ndu！」</t>
+          <t>「Then I'll do more... amu, chu, rero, reroryu...
+nnya, rerorerorero~... ndu！」</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -6007,8 +6012,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>「amuu... chu, dju！ djubu, bubu！ djubu... djubu！ pph...
-dju-ru！」</t>
+          <t>「amuu... chu, dju！ djubu, bubu！ djubu... djubu！
+pph... dju-ru！」</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6116,8 +6121,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>…I just can't hold my breath for long, so the momentum
-dies down.</t>
+          <t>…I just can't hold my breath for long, so the
+momentum dies down.</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6285,7 +6290,8 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>「Hey, why don't you try it like you're giving a kiss？」</t>
+          <t>「Hey, why don't you try it like you're giving a
+kiss？」</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6360,8 +6366,8 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>She kissed the tip, and a buzzing rush of pleasure ran
-through me.</t>
+          <t>She kissed the tip, and a buzzing rush of pleasure
+ran through me.</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6604,8 +6610,8 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>She's using everything I taught her, and still showing
-no mercy with her hands.</t>
+          <t>She's using everything I taught her, and still
+showing no mercy with her hands.</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6727,8 +6733,8 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>「Lero-leryu！ Ryu... dyu！ Dyuryu！ Nn... chu, chu！ Lero,
-lero... dyu！」</t>
+          <t>「Lero-leryu！ Ryu... dyu！ Dyuryu！ Nn... chu, chu！
+Lero, lero... dyu！」</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6896,8 +6902,8 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Oniichan, Hawaii~！ Nn... jyu, jyujyu！ Pp, rero
-rero rero！ Chuu！」</t>
+          <t>「Mmm... Oniichan, Hawaii~！ Nn... jyu, jyujyu！ Pp,
+rero rero rero！ Chuu！」</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6988,8 +6994,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu... jyu~ppu, jyububu！ Nn... jyubu, jyujyu！ Kuppu,
-gupa, pupuu...！」</t>
+          <t>「Nnnu... jyu~ppu, jyububu！ Nn... jyubu, jyujyu！
+Kuppu, gupa, pupuu...！」</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7081,8 +7087,8 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>「squish, squish！ kpp, brrju... jup！ n'ah... slrrrlick！
-smack！ smoo... slurp！」</t>
+          <t>「squish, squish！ kpp, brrju... jup！ n'ah...
+slrrrlick！ smack！ smoo... slurp！」</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7739,8 +7745,8 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan’s doing it in her own way, thinking about it
-and everything, but she’s doing something super
+          <t>Miru-chan’s doing it in her own way, thinking about
+it and everything, but she’s doing something super
 lewd...！</t>
         </is>
       </c>
@@ -8030,8 +8036,8 @@
       </c>
       <c r="B495" s="1" t="inlineStr">
         <is>
-          <t>I tried to hold back the feeling of coming, but it was
-already too late.</t>
+          <t>I tried to hold back the feeling of coming, but it
+was already too late.</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -8444,8 +8450,8 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>...Even so, my hands fumbled when wiping the semen off
-Miru-chan's face.</t>
+          <t>...Even so, my hands fumbled when wiping the semen
+off Miru-chan's face.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8688,8 +8694,8 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>Hearing that, I couldn't dodge it anymore, so I smiled
-instead.</t>
+          <t>Hearing that, I couldn't dodge it anymore, so I
+smiled instead.</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -9130,7 +9136,8 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Hey, you can still do the science project, you know？」</t>
+          <t>「Hey, you can still do the science project, you
+know？」</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9360,8 +9367,8 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>All things considered, everything turned out fine, and
-honestly it was a brilliant idea.</t>
+          <t>All things considered, everything turned out fine,
+and honestly it was a brilliant idea.</t>
         </is>
       </c>
       <c r="C582" t="n">

--- a/processed_ruby_restored_xlsx/sc242_みるく４：自由研究.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc242_みるく４：自由研究.ss.xlsx
@@ -1493,8 +1493,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>「N-No, it's not what you think！？ This is just a
-free-research notebook！」</t>
+          <t>N-No, it's not what you think！？ This is just a
+free-research notebook！</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Then I nimbly snatch the notebook away.</t>
+          <t>Then he nimbly snatches the notebook away.</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1661,8 +1661,8 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Just as Miru-chan reaches a boiling point, I simply
-hand the notebook back.</t>
+          <t>Just as Miru-chan reaches a boiling point, he simply
+hands the notebook back.</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1783,8 +1783,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>I repeat the question she'd dodged earlier, and this
-time she actually answers.</t>
+          <t>He repeats the question she'd dodged earlier, and
+this time she actually answers.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2627,9 +2627,9 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>When I took my underwear off and exposed my morning
-erection, Miru-chan murmured as if she couldn't
-believe it.</t>
+          <t>When he took his underwear off and exposed his
+morning erection, Miru-chan murmured as if she
+couldn't believe it.</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan stared intently at my penis.</t>
+          <t>Miru-chan stared intently at his penis.</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>After saying that, I silently ran my pencil across
+          <t>After saying that, he silently ran his pencil across
 the page.</t>
         </is>
       </c>
@@ -3593,8 +3593,8 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>「If you jerk off with your hand, you might have
-something to write about again, huh？」</t>
+          <t>If you jerk off with your hand, you might have
+something to write about again, huh？</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3792,7 +3792,7 @@
       <c r="B218" s="1" t="inlineStr">
         <is>
           <t>But then, as if she'd remembered something, she
-gently grabbed my penis.</t>
+gently grabbed his penis.</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3868,7 +3868,7 @@
       <c r="B223" s="1" t="inlineStr">
         <is>
           <t>When Miru-chan started moving her hand, a sound
-escaped me without meaning to.</t>
+escaped him without meaning to.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3946,8 +3946,8 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... when you rub it like that, you get off so
-easily, don't you...？」</t>
+          <t>Mmm... when you rub it like that, you get off so
+easily, don't you...？</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>「Nn... chupu... eheh！ Miru, am I doing it well？」</t>
+          <t>Nn... chupu... eheh！ Miru, am I doing it well？</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh...！」</t>
+          <t>Aahhh...！</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6367,7 +6367,7 @@
       <c r="B386" s="1" t="inlineStr">
         <is>
           <t>She kissed the tip, and a buzzing rush of pleasure
-ran through me.</t>
+ran through him.</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>「Oh, we only just kissed a little...」</t>
+          <t>Oh, we only just kissed a little...</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>「Oh... is that so？ That's your weak spot？」</t>
+          <t>Oh... is that so？ That's your weak spot？</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -6902,8 +6902,8 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Oniichan, Hawaii~！ Nn... jyu, jyujyu！ Pp,
-rero rero rero！ Chuu！」</t>
+          <t>Mmm... Oniichan, Hawaii~！ Nn... jyu, jyujyu！ Pp, rero
+rero rero！ Chuu！</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>「Uwaa...！」</t>
+          <t>Uwaa...！</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6994,8 +6994,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu... jyu~ppu, jyububu！ Nn... jyubu, jyujyu！
-Kuppu, gupa, pupuu...！」</t>
+          <t>Nnnu... jyu~ppu, jyububu！ Nn... jyubu, jyujyu！ Kuppu,
+gupa, pupuu...！</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>「Eah...？　Aah！」</t>
+          <t>Eah...？　Aah！</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7087,8 +7087,8 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>「squish, squish！ kpp, brrju... jup！ n'ah...
-slrrrlick！ smack！ smoo... slurp！」</t>
+          <t>squish, squish！ kpp, brrju... jup！ n'ah... slrrrlick！
+smack！ smoo... slurp！</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... ahp, pff, pwaa...！ Nnh, nh... fuu, fuuu...」</t>
+          <t>Nnngh... ahp, pff, pwaa...！ Nnh, nh... fuu, fuuu...</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>It feels so good to have me cum in my mouth...</t>
+          <t>It feels so good to have him cum in my mouth...</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>When those tightly closed lips clamp down on my
+          <t>When those tightly closed lips clamp down on his
 ejaculating dick, the sensation of ejaculating is
 amplified right there…！</t>
         </is>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn！ Nfu, nnu~！？」</t>
+          <t>Nn, nnn！ Nfu, nnu~！？</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>Then she looks at me and asks what I should do.</t>
+          <t>Then they look at me and ask what I should do.</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um... haha, just drink it, okay？」</t>
+          <t>Ah, um... haha, just drink it, okay？</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnnhh... I- I drank it, okay？」</t>
+          <t>Nn... nnnhh... I- I drank it, okay？</t>
         </is>
       </c>
       <c r="C478" t="n">
